--- a/output/pdf_financials_xlsx/WFC.xlsx
+++ b/output/pdf_financials_xlsx/WFC.xlsx
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.091776</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.197844</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>68.64638600000001</v>
+        <v>68.55461</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14.628334</v>
+        <v>14.43049</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>53.618082</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>74.499217</v>
+        <v>74.40744100000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19.822334</v>
+        <v>19.62449</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>59.238857</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.03910994299316</v>
+        <v>27.00580031298552</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>27.7964317426312</v>
+        <v>27.51899936551107</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>21.5522260733886</v>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -53482,7 +53482,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -55464,7 +55464,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">

--- a/output/pdf_financials_xlsx/WFC.xlsx
+++ b/output/pdf_financials_xlsx/WFC.xlsx
@@ -1129,10 +1129,10 @@
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.958983</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-3.15505</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1168,10 +1168,10 @@
         <v>-0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-28.435886</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>-0</v>
+        <v>0.930902</v>
       </c>
     </row>
     <row r="14">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>68.55461</v>
+        <v>72.513593</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14.43049</v>
+        <v>17.58554</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>53.618082</v>
@@ -2130,10 +2130,10 @@
         <v>29.086719</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>37.18273</v>
+        <v>65.618616</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>45.74999</v>
+        <v>44.819088</v>
       </c>
     </row>
     <row r="28">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>74.40744100000001</v>
+        <v>78.36642399999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19.62449</v>
+        <v>22.77954</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>59.238857</v>
@@ -2258,10 +2258,10 @@
         <v>41.864031</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>49.523909</v>
+        <v>77.959795</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>57.224328</v>
+        <v>56.293426</v>
       </c>
     </row>
     <row r="30">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.00580031298552</v>
+        <v>28.44269295307114</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>27.51899936551107</v>
+        <v>31.94325798054544</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>21.5522260733886</v>
@@ -2325,10 +2325,10 @@
         <v>26.973695138477</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>24.12446561670101</v>
+        <v>37.9763720582428</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.92526576010716</v>
+        <v>31.40591857359908</v>
       </c>
     </row>
     <row r="31">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>8.137499999999999</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -41334,7 +41334,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E328" s="5" t="n">
         <v>8.137499999999999</v>
       </c>
@@ -43686,7 +43690,11 @@
           <t>Net finance expense $ 29,366,788 $</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -56194,7 +56202,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WFC.xlsx
+++ b/output/pdf_financials_xlsx/WFC.xlsx
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>1.991481</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-2.984579</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1.049299</v>
+        <v>14.009368</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-11.595156</v>
@@ -7873,13 +7873,13 @@
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-2.643953</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-3.148812</v>
       </c>
       <c r="S121" s="3" t="n">
-        <v>0</v>
+        <v>-2.463578</v>
       </c>
     </row>
     <row r="122">
@@ -21896,7 +21896,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -24888,7 +24892,11 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -27844,7 +27852,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31390,7 +31402,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -36634,7 +36650,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -38002,7 +38022,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" s="5" t="n">
         <v>-5.685162</v>
       </c>
@@ -38520,7 +38544,11 @@
           <t>Changes in non-cash operating working capital (note 11)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>1.991481</v>
       </c>
